--- a/physician_forms/010_coronavirus_symptom_monitoring_form--physician_forms.xlsx
+++ b/physician_forms/010_coronavirus_symptom_monitoring_form--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sore_throat_choices</t>
+          <t>muscle_fatigue_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>muscle_weakness</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Muscle weakness</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>muscle_weakness</t>
+          <t>muscle_aches</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Muscle weakness</t>
+          <t>Muscle aches</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>muscle_aches</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Muscle aches</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>muscle_fatigue_choices</t>
+          <t>shortness_breath_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>difficulty_breathing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Difficulty breathing</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>difficulty_breathing</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Difficulty breathing</t>
+          <t>Shortness of breath</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>chest_tightness</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shortness of breath</t>
+          <t>Chest tightness</t>
         </is>
       </c>
     </row>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>chest_tightness</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chest tightness</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shortness_breath_choices</t>
+          <t>confusion_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>confusion</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Confusion</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>confusion</t>
+          <t>disorientation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Confusion</t>
+          <t>Disorientation</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>disorientation</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Disorientation</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>confusion_choices</t>
+          <t>chest_tightness_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>chest_tightness</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Chest tightness</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>chest_tightness</t>
+          <t>difficulty_breathing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chest tightness</t>
+          <t>Difficulty breathing</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>difficulty_breathing</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Difficulty breathing</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>chest_tightness_choices</t>
+          <t>loss_of_concentration_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>loss_of_concentration</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Loss of concentration</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>loss_of_concentration</t>
+          <t>confusion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Loss of concentration</t>
+          <t>Confusion</t>
         </is>
       </c>
     </row>
@@ -2032,29 +2032,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>confusion</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Confusion</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>loss_of_concentration_choices</t>
+          <t>memory_loss_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>difficulty_concentrating</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Difficulty concentrating</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>difficulty_concentrating</t>
+          <t>memory_loss</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Difficulty concentrating</t>
+          <t>Memory Loss</t>
         </is>
       </c>
     </row>
@@ -2083,29 +2083,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>memory_loss</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memory Loss</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>memory_loss_choices</t>
+          <t>irritability_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>irritability</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Irritability</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>irritability</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irritability</t>
+          <t>Anger</t>
         </is>
       </c>
     </row>
@@ -2134,29 +2134,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Anger</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>irritability_choices</t>
+          <t>other_symptoms_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other_symptoms</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other symptoms</t>
         </is>
       </c>
     </row>
@@ -2168,27 +2168,10 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>other_symptoms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
-        <is>
-          <t>Other symptoms</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>other_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
